--- a/WebApplication1/App_Data/DxWarmup/Compose/compose_warmup_source.xlsx
+++ b/WebApplication1/App_Data/DxWarmup/Compose/compose_warmup_source.xlsx
@@ -394,7 +394,7 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="C3" s="1">
-        <x:v>46195</x:v>
+        <x:v>46205</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
